--- a/producer/99pasal.xlsx
+++ b/producer/99pasal.xlsx
@@ -27,7 +27,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Image</t>
+    <t>Product Image</t>
   </si>
   <si>
     <t>Keychain/ mobile side bag black</t>
